--- a/재정학/03_Exams/[1] midterm/오후반 시험 결과 및 성적/재정학 오후반.xlsx
+++ b/재정학/03_Exams/[1] midterm/오후반 시험 결과 및 성적/재정학 오후반.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\03_Exams\오후반 시험 결과 및 성적\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\03_Exams\[1] midterm\오후반 시험 결과 및 성적\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7485E8C8-9677-4F2D-A0F2-5FD616444F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828E3D6E-1ABB-46D0-8214-E35F8E241614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">그래프!$B$4:$L$4</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">그래프!$F$5:$F$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="95">
   <si>
     <t>순번</t>
   </si>
@@ -306,23 +305,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>그래프 조금 그린 사람들</t>
+    <t>중간고사</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>강유현</t>
+    <t>기말고사</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>전혜성</t>
+    <t>총점</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>양성원</t>
+    <t>A+</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>김용빈</t>
+    <t>B+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -330,7 +337,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -341,6 +351,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -355,13 +366,45 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -376,10 +419,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -395,673 +444,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{EE83A279-147F-4974-BBEA-FB3F41A4572C}">
-          <cx:dataId val="0"/>
-          <cx:layoutPr>
-            <cx:binning intervalClosed="r">
-              <cx:binSize val="5"/>
-            </cx:binning>
-          </cx:layoutPr>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0"/>
-        <cx:tickLabels/>
-      </cx:axis>
-      <cx:axis id="1">
-        <cx:valScaling/>
-        <cx:majorGridlines/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>330199</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="차트 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2A25358-FE5E-FDA7-DED7-20EAAB90C063}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10925174" y="3213100"/>
-              <a:ext cx="7083425" cy="3365500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
-                <a:t>Excel 버전에서는 이 차트를 사용할 수 없습니다.
-이 도형 편집하거나 이 통합 문서를 다른 파일 형식으로 저장하면 차트가 영구적으로 손상됩니다.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2497,10 +1879,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D651A97-E656-4BDD-89B1-A84371D12C2B}">
-  <dimension ref="B4:O44"/>
+  <dimension ref="B1:T41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="4" spans="2:15" ht="17" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+      <c r="R1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S1">
+        <f>AVERAGE(F5:F41)</f>
+        <v>41.729729729729726</v>
+      </c>
+      <c r="T1">
+        <f>AVERAGE(G5:G41)</f>
+        <v>68.675675675675677</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+      <c r="R2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2">
+        <f>STDEV(F5:F41)</f>
+        <v>18.148918928086552</v>
+      </c>
+      <c r="T2">
+        <f>STDEV(G5:G41)</f>
+        <v>16.747809233273291</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="17" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2513,14 +1921,14 @@
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>6</v>
+      <c r="F4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>7</v>
@@ -2534,414 +1942,562 @@
       <c r="L4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="17" x14ac:dyDescent="0.45">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="2:20" ht="17" x14ac:dyDescent="0.45">
       <c r="B5">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>86</v>
+      </c>
+      <c r="G5">
+        <v>91</v>
+      </c>
+      <c r="H5">
+        <f>SUM(F5:G5)</f>
+        <v>177</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="Q5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>79.5</v>
+      </c>
+      <c r="G6">
+        <v>94</v>
+      </c>
+      <c r="H6">
+        <f>SUM(F6:G6)</f>
+        <v>173.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="Q6" s="8">
+        <v>11</v>
+      </c>
+      <c r="R6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>87</v>
+      </c>
+      <c r="H7">
+        <f>SUM(F7:G7)</f>
+        <v>161</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="Q7" s="8">
+        <v>14</v>
+      </c>
+      <c r="R7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>79</v>
+      </c>
+      <c r="G8">
+        <v>81</v>
+      </c>
+      <c r="H8">
+        <f>SUM(F8:G8)</f>
+        <v>160</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="Q8" s="8">
+        <v>12</v>
+      </c>
+      <c r="R8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>62</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <f>SUM(F9:G9)</f>
+        <v>154</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B10">
+        <v>35</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>73</v>
+      </c>
+      <c r="G10">
+        <v>70</v>
+      </c>
+      <c r="H10">
+        <f>SUM(F10:G10)</f>
+        <v>143</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>49.5</v>
+      </c>
+      <c r="G11">
+        <v>90</v>
+      </c>
+      <c r="H11">
+        <f>SUM(F11:G11)</f>
+        <v>139.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>51</v>
+      </c>
+      <c r="G12">
+        <v>85</v>
+      </c>
+      <c r="H12">
+        <f>SUM(F12:G12)</f>
+        <v>136</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>81.5</v>
+      </c>
+      <c r="H13">
+        <f>SUM(F13:G13)</f>
+        <v>134.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>51</v>
+      </c>
+      <c r="G14">
         <v>76</v>
       </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" ht="17" x14ac:dyDescent="0.45">
-      <c r="B6">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="H14">
+        <f>SUM(F14:G14)</f>
+        <v>127</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
         <v>48</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G15">
+        <v>78</v>
+      </c>
+      <c r="H15">
+        <f>SUM(F15:G15)</f>
+        <v>126</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B16">
+        <v>28</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <v>46.5</v>
+      </c>
+      <c r="G16">
+        <v>78</v>
+      </c>
+      <c r="H16">
+        <f>SUM(F16:G16)</f>
+        <v>124.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>17.5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="17" x14ac:dyDescent="0.45">
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="17" x14ac:dyDescent="0.45">
-      <c r="B8">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="s">
+      <c r="G17">
+        <v>69</v>
+      </c>
+      <c r="H17">
+        <f>SUM(F17:G17)</f>
+        <v>118</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>25.5</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11">
-        <v>28</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12">
-        <v>29.5</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13">
-        <v>29.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14">
-        <v>30</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15">
-        <v>30</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B18">
         <v>18</v>
       </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16">
-        <v>31</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17">
-        <v>31</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
+      <c r="C18" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>36.5</v>
+      </c>
+      <c r="G18">
+        <v>79</v>
+      </c>
+      <c r="H18">
+        <f>SUM(F18:G18)</f>
+        <v>115.5</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2955,12 +2511,15 @@
       <c r="L18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="M18" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>17</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
@@ -2972,6 +2531,13 @@
       <c r="F19">
         <v>34</v>
       </c>
+      <c r="G19">
+        <v>78</v>
+      </c>
+      <c r="H19">
+        <f>SUM(F19:G19)</f>
+        <v>112</v>
+      </c>
       <c r="I19">
         <v>0</v>
       </c>
@@ -2984,632 +2550,852 @@
       <c r="L19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="M19" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20">
+        <v>32</v>
+      </c>
+      <c r="G20">
+        <v>79</v>
+      </c>
+      <c r="H20">
+        <f>SUM(F20:G20)</f>
+        <v>111</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21">
+        <v>42.5</v>
+      </c>
+      <c r="G21">
+        <v>68.5</v>
+      </c>
+      <c r="H21">
+        <f>SUM(F21:G21)</f>
+        <v>111</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22">
+        <v>30</v>
+      </c>
+      <c r="G22">
+        <v>80</v>
+      </c>
+      <c r="H22">
+        <f>SUM(F22:G22)</f>
+        <v>110</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <v>37</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23">
+        <v>37.5</v>
+      </c>
+      <c r="G23">
+        <v>71</v>
+      </c>
+      <c r="H23">
+        <f>SUM(F23:G23)</f>
+        <v>108.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <v>40</v>
+      </c>
+      <c r="G24">
+        <v>67</v>
+      </c>
+      <c r="H24">
+        <f>SUM(F24:G24)</f>
+        <v>107</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <v>30</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25">
+        <v>30</v>
+      </c>
+      <c r="G25">
+        <v>76</v>
+      </c>
+      <c r="H25">
+        <f>SUM(F25:G25)</f>
+        <v>106</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B26">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26">
+        <v>37</v>
+      </c>
+      <c r="G26">
+        <v>64.5</v>
+      </c>
+      <c r="H26">
+        <f>SUM(F26:G26)</f>
+        <v>101.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27">
+        <v>28</v>
+      </c>
+      <c r="G27">
+        <v>72</v>
+      </c>
+      <c r="H27">
+        <f>SUM(F27:G27)</f>
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <v>29.5</v>
+      </c>
+      <c r="G28">
+        <v>68.5</v>
+      </c>
+      <c r="H28">
+        <f>SUM(F28:G28)</f>
+        <v>98</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D29" t="s">
         <v>17</v>
       </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20">
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29">
         <v>35</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21">
+      <c r="G29">
+        <v>62</v>
+      </c>
+      <c r="H29">
+        <f>SUM(F29:G29)</f>
+        <v>97</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <v>25.5</v>
+      </c>
+      <c r="G30">
+        <v>71</v>
+      </c>
+      <c r="H30">
+        <f>SUM(F30:G30)</f>
+        <v>96.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31">
+        <v>40</v>
+      </c>
+      <c r="G31">
+        <v>55.5</v>
+      </c>
+      <c r="H31">
+        <f>SUM(F31:G31)</f>
+        <v>95.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>31</v>
+      </c>
+      <c r="G32">
+        <v>63</v>
+      </c>
+      <c r="H32">
+        <f>SUM(F32:G32)</f>
+        <v>94</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B33">
+        <v>27</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <v>39</v>
+      </c>
+      <c r="G33">
+        <v>51</v>
+      </c>
+      <c r="H33">
+        <f>SUM(F33:G33)</f>
+        <v>90</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34">
+        <v>24</v>
+      </c>
+      <c r="G34">
+        <v>63.5</v>
+      </c>
+      <c r="H34">
+        <f>SUM(F34:G34)</f>
+        <v>87.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35">
+        <v>37</v>
+      </c>
+      <c r="G35">
+        <v>49</v>
+      </c>
+      <c r="H35">
+        <f>SUM(F35:G35)</f>
+        <v>86</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36">
+        <v>29.5</v>
+      </c>
+      <c r="G36">
+        <v>53</v>
+      </c>
+      <c r="H36">
+        <f>SUM(F36:G36)</f>
+        <v>82.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37">
+        <v>15</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>54</v>
+      </c>
+      <c r="H37">
+        <f>SUM(F37:G37)</f>
+        <v>75</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <v>19</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <v>17.5</v>
+      </c>
+      <c r="G38">
+        <v>52</v>
+      </c>
+      <c r="H38">
+        <f>SUM(F38:G38)</f>
+        <v>69.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21">
-        <v>36.5</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39">
+        <v>31</v>
+      </c>
+      <c r="G39">
         <v>36</v>
       </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22">
-        <v>37</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23">
-        <v>37</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24">
-        <v>37.5</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25">
-        <v>39</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26">
-        <v>40</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27">
-        <v>40</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28">
-        <v>74</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29">
-        <v>42.5</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="H39">
+        <f>SUM(F39:G39)</f>
         <v>67</v>
       </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30">
-        <v>46.5</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40">
         <v>23</v>
       </c>
-      <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31">
-        <v>48</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32">
-        <v>49</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B33">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>35</v>
+      </c>
+      <c r="H40">
+        <f>SUM(F40:G40)</f>
+        <v>60</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <v>33</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
         <v>20</v>
       </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33">
-        <v>49.5</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B34">
-        <v>8</v>
-      </c>
-      <c r="C34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34">
-        <v>51</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B35">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35">
-        <v>51</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B36">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="H41">
+        <f>SUM(F41:G41)</f>
         <v>30</v>
       </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36">
-        <v>53</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B37">
-        <v>32</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37">
-        <v>62</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B38">
-        <v>35</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38">
-        <v>73</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39">
-        <v>79</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B40">
-        <v>20</v>
-      </c>
-      <c r="C40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40">
-        <v>79.5</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B41">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41">
-        <v>86</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
@@ -3622,33 +3408,17 @@
       <c r="L41">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" ht="17" x14ac:dyDescent="0.45">
-      <c r="F43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G43">
-        <f>AVERAGE(F5:F41)</f>
-        <v>41.729729729729726</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" ht="17" x14ac:dyDescent="0.45">
-      <c r="F44" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G44">
-        <f>STDEV(F5:F41)</f>
-        <v>18.148918928086552</v>
+      <c r="M41" s="7" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:L4" xr:uid="{2D651A97-E656-4BDD-89B1-A84371D12C2B}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:L41">
-      <sortCondition ref="F4"/>
+      <sortCondition descending="1" ref="H4"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/재정학/03_Exams/[1] midterm/오후반 시험 결과 및 성적/재정학 오후반.xlsx
+++ b/재정학/03_Exams/[1] midterm/오후반 시험 결과 및 성적/재정학 오후반.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\03_Exams\[1] midterm\오후반 시험 결과 및 성적\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828E3D6E-1ABB-46D0-8214-E35F8E241614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFC21B5-4AD2-4B92-BD02-327E2E5BA7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57495" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
     <sheet name="그래프" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">그래프!$B$4:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">그래프!$A$4:$J$4</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">그래프!$G$5:$G$41</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">그래프!$H$5:$H$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>순번</t>
   </si>
@@ -329,7 +331,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C0</t>
+    <t>100환산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠진시간</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출석시간</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1879,1543 +1889,1503 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D651A97-E656-4BDD-89B1-A84371D12C2B}">
-  <dimension ref="B1:T41"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="R1" s="2" t="s">
+    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="P1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="S1">
+      <c r="Q1">
+        <f>AVERAGE(E5:E41)</f>
+        <v>41.729729729729726</v>
+      </c>
+      <c r="R1">
         <f>AVERAGE(F5:F41)</f>
-        <v>41.729729729729726</v>
-      </c>
-      <c r="T1">
-        <f>AVERAGE(G5:G41)</f>
         <v>68.675675675675677</v>
       </c>
     </row>
-    <row r="2" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="R2" s="2" t="s">
+    <row r="2" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="P2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="S2">
+      <c r="Q2">
+        <f>STDEV(E5:E41)</f>
+        <v>18.148918928086552</v>
+      </c>
+      <c r="R2">
         <f>STDEV(F5:F41)</f>
-        <v>18.148918928086552</v>
-      </c>
-      <c r="T2">
-        <f>STDEV(G5:G41)</f>
         <v>16.747809233273291</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>86</v>
+      </c>
+      <c r="F5">
+        <v>91</v>
+      </c>
+      <c r="G5">
+        <f>SUM(E5:F5)</f>
+        <v>177</v>
+      </c>
+      <c r="H5">
+        <f>G5/2</f>
+        <v>88.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>45-I5</f>
+        <v>45</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="O5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>79.5</v>
+      </c>
+      <c r="F6">
+        <v>94</v>
+      </c>
+      <c r="G6">
+        <f>SUM(E6:F6)</f>
+        <v>173.5</v>
+      </c>
+      <c r="H6">
+        <f>G6/2</f>
+        <v>86.75</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>45-I6</f>
+        <v>45</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="O6" s="8">
+        <v>11</v>
+      </c>
+      <c r="P6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>74</v>
+      </c>
+      <c r="F7">
+        <v>87</v>
+      </c>
+      <c r="G7">
+        <f>SUM(E7:F7)</f>
+        <v>161</v>
+      </c>
+      <c r="H7">
+        <f>G7/2</f>
+        <v>80.5</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <f>45-I7</f>
+        <v>42</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="O7" s="8">
+        <v>14</v>
+      </c>
+      <c r="P7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="17" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>79</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8">
+        <f>SUM(E8:F8)</f>
+        <v>160</v>
+      </c>
+      <c r="H8">
+        <f>G8/2</f>
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>45-I8</f>
+        <v>45</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="O8" s="8">
+        <v>12</v>
+      </c>
+      <c r="P8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>62</v>
+      </c>
+      <c r="F9">
+        <v>92</v>
+      </c>
+      <c r="G9">
+        <f>SUM(E9:F9)</f>
+        <v>154</v>
+      </c>
+      <c r="H9">
+        <f>G9/2</f>
+        <v>77</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>45-I9</f>
+        <v>45</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>73</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <f>SUM(E10:F10)</f>
+        <v>143</v>
+      </c>
+      <c r="H10">
+        <f>G10/2</f>
+        <v>71.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>45-I10</f>
+        <v>45</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>49.5</v>
+      </c>
+      <c r="F11">
+        <v>90</v>
+      </c>
+      <c r="G11">
+        <f>SUM(E11:F11)</f>
+        <v>139.5</v>
+      </c>
+      <c r="H11">
+        <f>G11/2</f>
+        <v>69.75</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>45-I11</f>
+        <v>45</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12">
+        <v>51</v>
+      </c>
+      <c r="F12">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <f>SUM(E12:F12)</f>
+        <v>136</v>
+      </c>
+      <c r="H12">
+        <f>G12/2</f>
+        <v>68</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>45-I12</f>
+        <v>45</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>53</v>
+      </c>
+      <c r="F13">
+        <v>81.5</v>
+      </c>
+      <c r="G13">
+        <f>SUM(E13:F13)</f>
+        <v>134.5</v>
+      </c>
+      <c r="H13">
+        <f>G13/2</f>
+        <v>67.25</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>45-I13</f>
+        <v>45</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>51</v>
+      </c>
+      <c r="F14">
+        <v>76</v>
+      </c>
+      <c r="G14">
+        <f>SUM(E14:F14)</f>
+        <v>127</v>
+      </c>
+      <c r="H14">
+        <f>G14/2</f>
+        <v>63.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>45-I14</f>
+        <v>45</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>78</v>
+      </c>
+      <c r="G15">
+        <f>SUM(E15:F15)</f>
+        <v>126</v>
+      </c>
+      <c r="H15">
+        <f>G15/2</f>
+        <v>63</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <f>45-I15</f>
+        <v>42</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16">
+        <v>46.5</v>
+      </c>
+      <c r="F16">
+        <v>78</v>
+      </c>
+      <c r="G16">
+        <f>SUM(E16:F16)</f>
+        <v>124.5</v>
+      </c>
+      <c r="H16">
+        <f>G16/2</f>
+        <v>62.25</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <f>45-I16</f>
+        <v>42</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>49</v>
+      </c>
+      <c r="F17">
+        <v>69</v>
+      </c>
+      <c r="G17">
+        <f>SUM(E17:F17)</f>
+        <v>118</v>
+      </c>
+      <c r="H17">
+        <f>G17/2</f>
+        <v>59</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <f>45-I17</f>
+        <v>39</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>36.5</v>
+      </c>
+      <c r="F18">
+        <v>79</v>
+      </c>
+      <c r="G18">
+        <f>SUM(E18:F18)</f>
+        <v>115.5</v>
+      </c>
+      <c r="H18">
+        <f>G18/2</f>
+        <v>57.75</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f>45-I18</f>
+        <v>45</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19">
+        <v>34</v>
+      </c>
+      <c r="F19">
+        <v>78</v>
+      </c>
+      <c r="G19">
+        <f>SUM(E19:F19)</f>
+        <v>112</v>
+      </c>
+      <c r="H19">
+        <f>G19/2</f>
+        <v>56</v>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19">
+        <f>45-I19</f>
+        <v>39</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>25</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20">
+        <v>32</v>
+      </c>
+      <c r="F20">
+        <v>79</v>
+      </c>
+      <c r="G20">
+        <f>SUM(E20:F20)</f>
+        <v>111</v>
+      </c>
+      <c r="H20">
+        <f>G20/2</f>
+        <v>55.5</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <f>45-I20</f>
+        <v>38</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>9</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21">
+        <v>42.5</v>
+      </c>
+      <c r="F21">
+        <v>68.5</v>
+      </c>
+      <c r="G21">
+        <f>SUM(E21:F21)</f>
+        <v>111</v>
+      </c>
+      <c r="H21">
+        <f>G21/2</f>
+        <v>55.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f>45-I21</f>
+        <v>45</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>80</v>
+      </c>
+      <c r="G22">
+        <f>SUM(E22:F22)</f>
+        <v>110</v>
+      </c>
+      <c r="H22">
+        <f>G22/2</f>
+        <v>55</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f>45-I22</f>
+        <v>45</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23">
+        <v>37.5</v>
+      </c>
+      <c r="F23">
+        <v>71</v>
+      </c>
+      <c r="G23">
+        <f>SUM(E23:F23)</f>
+        <v>108.5</v>
+      </c>
+      <c r="H23">
+        <f>G23/2</f>
+        <v>54.25</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="J23">
+        <f>45-I23</f>
+        <v>39</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>67</v>
+      </c>
+      <c r="G24">
+        <f>SUM(E24:F24)</f>
+        <v>107</v>
+      </c>
+      <c r="H24">
+        <f>G24/2</f>
+        <v>53.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f>45-I24</f>
+        <v>45</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>30</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>76</v>
+      </c>
+      <c r="G25">
+        <f>SUM(E25:F25)</f>
+        <v>106</v>
+      </c>
+      <c r="H25">
+        <f>G25/2</f>
+        <v>53</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f>45-I25</f>
+        <v>45</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>13</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26">
+        <v>37</v>
+      </c>
+      <c r="F26">
+        <v>64.5</v>
+      </c>
+      <c r="G26">
+        <f>SUM(E26:F26)</f>
+        <v>101.5</v>
+      </c>
+      <c r="H26">
+        <f>G26/2</f>
+        <v>50.75</v>
+      </c>
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="J26">
+        <f>45-I26</f>
+        <v>43</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>28</v>
+      </c>
+      <c r="F27">
+        <v>72</v>
+      </c>
+      <c r="G27">
+        <f>SUM(E27:F27)</f>
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <f>G27/2</f>
+        <v>50</v>
+      </c>
+      <c r="I27">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="J27">
+        <f>45-I27</f>
+        <v>42</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>31</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>29.5</v>
+      </c>
+      <c r="F28">
+        <v>68.5</v>
+      </c>
+      <c r="G28">
+        <f>SUM(E28:F28)</f>
+        <v>98</v>
+      </c>
+      <c r="H28">
+        <f>G28/2</f>
+        <v>49</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <f>45-I28</f>
+        <v>42</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>35</v>
+      </c>
+      <c r="F29">
+        <v>62</v>
+      </c>
+      <c r="G29">
+        <f>SUM(E29:F29)</f>
+        <v>97</v>
+      </c>
+      <c r="H29">
+        <f>G29/2</f>
+        <v>48.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f>45-I29</f>
+        <v>45</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>11</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>25.5</v>
+      </c>
+      <c r="F30">
+        <v>71</v>
+      </c>
+      <c r="G30">
+        <f>SUM(E30:F30)</f>
+        <v>96.5</v>
+      </c>
+      <c r="H30">
+        <f>G30/2</f>
+        <v>48.25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f>45-I30</f>
+        <v>45</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>24</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>40</v>
+      </c>
+      <c r="F31">
+        <v>55.5</v>
+      </c>
+      <c r="G31">
+        <f>SUM(E31:F31)</f>
+        <v>95.5</v>
+      </c>
+      <c r="H31">
+        <f>G31/2</f>
+        <v>47.75</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <f>45-I31</f>
+        <v>45</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>16</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>63</v>
+      </c>
+      <c r="G32">
+        <f>SUM(E32:F32)</f>
+        <v>94</v>
+      </c>
+      <c r="H32">
+        <f>G32/2</f>
+        <v>47</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <f>45-I32</f>
+        <v>42</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33">
+        <v>39</v>
+      </c>
+      <c r="F33">
+        <v>51</v>
+      </c>
+      <c r="G33">
+        <f>SUM(E33:F33)</f>
         <v>90</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="H33">
+        <f>G33/2</f>
+        <v>45</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <f>45-I33</f>
+        <v>42</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>36</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>24</v>
+      </c>
+      <c r="F34">
+        <v>63.5</v>
+      </c>
+      <c r="G34">
+        <f>SUM(E34:F34)</f>
+        <v>87.5</v>
+      </c>
+      <c r="H34">
+        <f>G34/2</f>
+        <v>43.75</v>
+      </c>
+      <c r="I34">
+        <v>6</v>
+      </c>
+      <c r="J34">
+        <f>45-I34</f>
+        <v>39</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35">
+        <v>37</v>
+      </c>
+      <c r="F35">
+        <v>49</v>
+      </c>
+      <c r="G35">
+        <f>SUM(E35:F35)</f>
+        <v>86</v>
+      </c>
+      <c r="H35">
+        <f>G35/2</f>
+        <v>43</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f>45-I35</f>
+        <v>45</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>29</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36">
+        <v>29.5</v>
+      </c>
+      <c r="F36">
+        <v>53</v>
+      </c>
+      <c r="G36">
+        <f>SUM(E36:F36)</f>
+        <v>82.5</v>
+      </c>
+      <c r="H36">
+        <f>G36/2</f>
+        <v>41.25</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f>45-I36</f>
+        <v>45</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>15</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37">
+        <v>21</v>
+      </c>
+      <c r="F37">
+        <v>54</v>
+      </c>
+      <c r="G37">
+        <f>SUM(E37:F37)</f>
+        <v>75</v>
+      </c>
+      <c r="H37">
+        <f>G37/2</f>
+        <v>37.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <f>45-I37</f>
+        <v>45</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>19</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>17.5</v>
+      </c>
+      <c r="F38">
+        <v>52</v>
+      </c>
+      <c r="G38">
+        <f>SUM(E38:F38)</f>
+        <v>69.5</v>
+      </c>
+      <c r="H38">
+        <f>G38/2</f>
+        <v>34.75</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <f>45-I38</f>
+        <v>45</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>31</v>
+      </c>
+      <c r="F39">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <f>SUM(E39:F39)</f>
+        <v>67</v>
+      </c>
+      <c r="H39">
+        <f>G39/2</f>
+        <v>33.5</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <f>45-I39</f>
+        <v>42</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>23</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40">
+        <v>25</v>
+      </c>
+      <c r="F40">
+        <v>35</v>
+      </c>
+      <c r="G40">
+        <f>SUM(E40:F40)</f>
+        <v>60</v>
+      </c>
+      <c r="H40">
+        <f>G40/2</f>
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <f>45-I40</f>
+        <v>45</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>33</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41">
         <v>10</v>
       </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>86</v>
-      </c>
-      <c r="G5">
-        <v>91</v>
-      </c>
-      <c r="H5">
-        <f>SUM(F5:G5)</f>
-        <v>177</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="Q5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="B6">
+      <c r="F41">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>79.5</v>
-      </c>
-      <c r="G6">
-        <v>94</v>
-      </c>
-      <c r="H6">
-        <f>SUM(F6:G6)</f>
-        <v>173.5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="Q6" s="8">
-        <v>11</v>
-      </c>
-      <c r="R6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>74</v>
-      </c>
-      <c r="G7">
-        <v>87</v>
-      </c>
-      <c r="H7">
-        <f>SUM(F7:G7)</f>
-        <v>161</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="Q7" s="8">
-        <v>14</v>
-      </c>
-      <c r="R7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:20" ht="17" x14ac:dyDescent="0.45">
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G41">
+        <f>SUM(E41:F41)</f>
+        <v>30</v>
+      </c>
+      <c r="H41">
+        <f>G41/2</f>
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>79</v>
-      </c>
-      <c r="G8">
-        <v>81</v>
-      </c>
-      <c r="H8">
-        <f>SUM(F8:G8)</f>
-        <v>160</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="Q8" s="8">
-        <v>12</v>
-      </c>
-      <c r="R8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <f>SUM(F9:G9)</f>
-        <v>154</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10">
-        <v>35</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>73</v>
-      </c>
-      <c r="G10">
-        <v>70</v>
-      </c>
-      <c r="H10">
-        <f>SUM(F10:G10)</f>
-        <v>143</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11">
-        <v>49.5</v>
-      </c>
-      <c r="G11">
-        <v>90</v>
-      </c>
-      <c r="H11">
-        <f>SUM(F11:G11)</f>
-        <v>139.5</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>85</v>
-      </c>
-      <c r="H12">
-        <f>SUM(F12:G12)</f>
-        <v>136</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>81.5</v>
-      </c>
-      <c r="H13">
-        <f>SUM(F13:G13)</f>
-        <v>134.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>76</v>
-      </c>
-      <c r="H14">
-        <f>SUM(F14:G14)</f>
-        <v>127</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>78</v>
-      </c>
-      <c r="H15">
-        <f>SUM(F15:G15)</f>
-        <v>126</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B16">
-        <v>28</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16">
-        <v>46.5</v>
-      </c>
-      <c r="G16">
-        <v>78</v>
-      </c>
-      <c r="H16">
-        <f>SUM(F16:G16)</f>
-        <v>124.5</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17">
-        <v>49</v>
-      </c>
-      <c r="G17">
-        <v>69</v>
-      </c>
-      <c r="H17">
-        <f>SUM(F17:G17)</f>
-        <v>118</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B18">
-        <v>18</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18">
-        <v>36.5</v>
-      </c>
-      <c r="G18">
-        <v>79</v>
-      </c>
-      <c r="H18">
-        <f>SUM(F18:G18)</f>
-        <v>115.5</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19">
-        <v>34</v>
-      </c>
-      <c r="G19">
-        <v>78</v>
-      </c>
-      <c r="H19">
-        <f>SUM(F19:G19)</f>
-        <v>112</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B20">
-        <v>25</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20">
-        <v>32</v>
-      </c>
-      <c r="G20">
-        <v>79</v>
-      </c>
-      <c r="H20">
-        <f>SUM(F20:G20)</f>
-        <v>111</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B21">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21">
-        <v>42.5</v>
-      </c>
-      <c r="G21">
-        <v>68.5</v>
-      </c>
-      <c r="H21">
-        <f>SUM(F21:G21)</f>
-        <v>111</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22">
-        <v>30</v>
-      </c>
-      <c r="G22">
-        <v>80</v>
-      </c>
-      <c r="H22">
-        <f>SUM(F22:G22)</f>
-        <v>110</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B23">
-        <v>37</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23">
-        <v>37.5</v>
-      </c>
-      <c r="G23">
-        <v>71</v>
-      </c>
-      <c r="H23">
-        <f>SUM(F23:G23)</f>
-        <v>108.5</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24">
-        <v>40</v>
-      </c>
-      <c r="G24">
-        <v>67</v>
-      </c>
-      <c r="H24">
-        <f>SUM(F24:G24)</f>
-        <v>107</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <v>30</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25">
-        <v>30</v>
-      </c>
-      <c r="G25">
-        <v>76</v>
-      </c>
-      <c r="H25">
-        <f>SUM(F25:G25)</f>
-        <v>106</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26">
-        <v>37</v>
-      </c>
-      <c r="G26">
-        <v>64.5</v>
-      </c>
-      <c r="H26">
-        <f>SUM(F26:G26)</f>
-        <v>101.5</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>26</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27">
-        <v>28</v>
-      </c>
-      <c r="G27">
-        <v>72</v>
-      </c>
-      <c r="H27">
-        <f>SUM(F27:G27)</f>
-        <v>100</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B28">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28">
-        <v>29.5</v>
-      </c>
-      <c r="G28">
-        <v>68.5</v>
-      </c>
-      <c r="H28">
-        <f>SUM(F28:G28)</f>
-        <v>98</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B29">
+      <c r="I41">
         <v>3</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29">
-        <v>35</v>
-      </c>
-      <c r="G29">
-        <v>62</v>
-      </c>
-      <c r="H29">
-        <f>SUM(F29:G29)</f>
-        <v>97</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B30">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30">
-        <v>25.5</v>
-      </c>
-      <c r="G30">
-        <v>71</v>
-      </c>
-      <c r="H30">
-        <f>SUM(F30:G30)</f>
-        <v>96.5</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B31">
-        <v>24</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31">
-        <v>40</v>
-      </c>
-      <c r="G31">
-        <v>55.5</v>
-      </c>
-      <c r="H31">
-        <f>SUM(F31:G31)</f>
-        <v>95.5</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" s="7" t="s">
+      <c r="J41">
+        <f>45-I41</f>
+        <v>42</v>
+      </c>
+      <c r="K41" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B32">
-        <v>16</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32">
-        <v>31</v>
-      </c>
-      <c r="G32">
-        <v>63</v>
-      </c>
-      <c r="H32">
-        <f>SUM(F32:G32)</f>
-        <v>94</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B33">
-        <v>27</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33">
-        <v>39</v>
-      </c>
-      <c r="G33">
-        <v>51</v>
-      </c>
-      <c r="H33">
-        <f>SUM(F33:G33)</f>
-        <v>90</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B34">
-        <v>36</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34">
-        <v>24</v>
-      </c>
-      <c r="G34">
-        <v>63.5</v>
-      </c>
-      <c r="H34">
-        <f>SUM(F34:G34)</f>
-        <v>87.5</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B35">
-        <v>34</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35">
-        <v>37</v>
-      </c>
-      <c r="G35">
-        <v>49</v>
-      </c>
-      <c r="H35">
-        <f>SUM(F35:G35)</f>
-        <v>86</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B36">
-        <v>29</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36">
-        <v>29.5</v>
-      </c>
-      <c r="G36">
-        <v>53</v>
-      </c>
-      <c r="H36">
-        <f>SUM(F36:G36)</f>
-        <v>82.5</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B37">
-        <v>15</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37">
-        <v>21</v>
-      </c>
-      <c r="G37">
-        <v>54</v>
-      </c>
-      <c r="H37">
-        <f>SUM(F37:G37)</f>
-        <v>75</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B38">
-        <v>19</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38">
-        <v>17.5</v>
-      </c>
-      <c r="G38">
-        <v>52</v>
-      </c>
-      <c r="H38">
-        <f>SUM(F38:G38)</f>
-        <v>69.5</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B39">
-        <v>4</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39">
-        <v>31</v>
-      </c>
-      <c r="G39">
-        <v>36</v>
-      </c>
-      <c r="H39">
-        <f>SUM(F39:G39)</f>
-        <v>67</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B40">
-        <v>23</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40">
-        <v>25</v>
-      </c>
-      <c r="G40">
-        <v>35</v>
-      </c>
-      <c r="H40">
-        <f>SUM(F40:G40)</f>
-        <v>60</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B41">
-        <v>33</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>77</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41">
-        <v>20</v>
-      </c>
-      <c r="H41">
-        <f>SUM(F41:G41)</f>
-        <v>30</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B4:L4" xr:uid="{2D651A97-E656-4BDD-89B1-A84371D12C2B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:L41">
-      <sortCondition descending="1" ref="H4"/>
+  <autoFilter ref="A4:J4" xr:uid="{2D651A97-E656-4BDD-89B1-A84371D12C2B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:J41">
+      <sortCondition descending="1" ref="G4"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
